--- a/REPORTE_DE_VENTAS_AJRO_HOUSE OFICIAL.xlsx
+++ b/REPORTE_DE_VENTAS_AJRO_HOUSE OFICIAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleja\OneDrive\Desktop\Perfume's Point STUFF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1A4896-05D0-4DC9-82D6-692FADDA3120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBD7C56-2105-4098-A067-2B46BA9036F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro de Inventario" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="95">
   <si>
     <t>AJRO HOUSE — INVENTARIO DE PERFUMES</t>
   </si>
@@ -318,6 +318,15 @@
   <si>
     <t>Keivy</t>
   </si>
+  <si>
+    <t>Monica Oliva</t>
+  </si>
+  <si>
+    <t>CAROLINA HERRERA GOOD GIRL BLACK</t>
+  </si>
+  <si>
+    <t>El cliente tiene opcion de 3 pagos 1266 lps c/u</t>
+  </si>
 </sst>
 </file>
 
@@ -547,18 +556,18 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -819,6 +828,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -870,6 +884,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -921,6 +940,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -972,6 +996,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1023,6 +1052,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1074,6 +1108,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1128,6 +1167,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1182,6 +1226,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1236,6 +1285,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1290,6 +1344,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1344,6 +1403,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-69F1-495A-A056-4E5BC19801B8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2617,7 +2681,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -2631,7 +2695,7 @@
       <c r="J1" s="20"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="20"/>
@@ -8453,7 +8517,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="20"/>
@@ -8467,7 +8531,7 @@
       <c r="J1" s="20"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="20"/>
@@ -8515,7 +8579,7 @@
     <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f t="shared" ref="A5:A14" ca="1" si="0">IF(B5="","",TODAY())</f>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>21</v>
@@ -8550,7 +8614,7 @@
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>25</v>
@@ -8585,7 +8649,7 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>29</v>
@@ -8620,7 +8684,7 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>30</v>
@@ -8655,7 +8719,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>31</v>
@@ -8690,7 +8754,7 @@
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>32</v>
@@ -8725,7 +8789,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>34</v>
@@ -8760,7 +8824,7 @@
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>36</v>
@@ -8795,7 +8859,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>39</v>
@@ -8830,7 +8894,7 @@
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>40</v>
@@ -8933,7 +8997,7 @@
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" ref="A17:A80" ca="1" si="3">IF(B17="","",TODAY())</f>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>43</v>
@@ -8966,7 +9030,7 @@
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>43</v>
@@ -8999,7 +9063,7 @@
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>43</v>
@@ -9032,7 +9096,7 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>43</v>
@@ -9065,7 +9129,7 @@
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>43</v>
@@ -9098,7 +9162,7 @@
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>43</v>
@@ -9131,7 +9195,7 @@
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>43</v>
@@ -9164,7 +9228,7 @@
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>43</v>
@@ -9197,7 +9261,7 @@
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>43</v>
@@ -9230,7 +9294,7 @@
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>31</v>
@@ -9265,7 +9329,7 @@
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>21</v>
@@ -9298,25 +9362,39 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="str">
+      <c r="A28" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6" t="str">
+        <v>46296</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="5">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6">
+        <v>3800</v>
+      </c>
+      <c r="G28" s="6">
+        <v>1266</v>
+      </c>
+      <c r="H28" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2534</v>
       </c>
       <c r="I28" s="5" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J28" s="5"/>
+        <v>CRÉDITO</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="str">
@@ -19375,7 +19453,7 @@
       </c>
       <c r="B3" s="9">
         <f>SUM('Registro de Ventas'!F5:F504)</f>
-        <v>9660</v>
+        <v>13460</v>
       </c>
       <c r="D3" t="s">
         <v>55</v>
@@ -19390,7 +19468,7 @@
       </c>
       <c r="B4" s="9">
         <f>SUM('Registro de Ventas'!G5:G504)</f>
-        <v>4525</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19399,7 +19477,7 @@
       </c>
       <c r="B5" s="9">
         <f>SUM('Registro de Ventas'!H5:H504)</f>
-        <v>5135</v>
+        <v>7669</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19408,7 +19486,7 @@
       </c>
       <c r="B6" s="9">
         <f>COUNTIF('Registro de Ventas'!B5:B504,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19417,7 +19495,7 @@
       </c>
       <c r="B7" s="9">
         <f>COUNTIF('Registro de Ventas'!I5:I504,"CRÉDITO")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -19722,21 +19800,24 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
       <c r="B25" s="11">
         <f>SUMIF('Registro de Ventas'!B$5:B$504,A25,'Registro de Ventas'!F$5:F$504)</f>
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="C25" s="11">
         <f>SUMIF('Registro de Ventas'!B$5:B$504,A25,'Registro de Ventas'!G$5:G$504)</f>
-        <v>0</v>
+        <v>1266</v>
       </c>
       <c r="D25" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2534</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="5"/>
-        <v>AL DÍA</v>
+        <v>PENDIENTE</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -19888,11 +19969,11 @@
         <v>1000</v>
       </c>
       <c r="D4" s="13">
-        <f t="shared" ref="D4:D12" si="0">MAX(B4-C4,0)</f>
+        <f t="shared" ref="D4:D13" si="0">MAX(B4-C4,0)</f>
         <v>3260</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" ref="E4:E12" si="1">IF(D4=0,"AL DÍA","PENDIENTE")</f>
+        <f t="shared" ref="E4:E13" si="1">IF(D4=0,"AL DÍA","PENDIENTE")</f>
         <v>PENDIENTE</v>
       </c>
     </row>
@@ -20065,14 +20146,46 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="13">
+        <f>SUMIF('Registro de Ventas'!B$5:B$504,A13,'Registro de Ventas'!F$5:F$504)</f>
+        <v>3800</v>
+      </c>
+      <c r="C13" s="13">
+        <f>SUMIF('Registro de Ventas'!B$5:B$504,A13,'Registro de Ventas'!G$5:G$504)</f>
+        <v>1266</v>
+      </c>
+      <c r="D13" s="13">
+        <f t="shared" si="0"/>
+        <v>2534</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="1"/>
+        <v>PENDIENTE</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="13">
+        <f>SUMIF('Registro de Ventas'!B$5:B$504,A14,'Registro de Ventas'!F$5:F$504)</f>
+        <v>1875</v>
+      </c>
+      <c r="C14" s="13">
+        <f>SUMIF('Registro de Ventas'!B$5:B$504,A14,'Registro de Ventas'!G$5:G$504)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
+        <f t="shared" ref="D14" si="2">MAX(B14-C14,0)</f>
+        <v>1875</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" ref="E14" si="3">IF(D14=0,"AL DÍA","PENDIENTE")</f>
+        <v>PENDIENTE</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
